--- a/docs/ValueSet-BRCategoriaAgenteAlergiasReacoesAdversas-1.0.xlsx
+++ b/docs/ValueSet-BRCategoriaAgenteAlergiasReacoesAdversas-1.0.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +73,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -105,40 +106,43 @@
     <t>food</t>
   </si>
   <si>
-    <t>Alimento</t>
+    <t>Food</t>
   </si>
   <si>
     <t>medication</t>
   </si>
   <si>
-    <t>Medicamento</t>
+    <t>Medication</t>
   </si>
   <si>
     <t>biologic</t>
   </si>
   <si>
-    <t>Biológica</t>
+    <t>Biologic</t>
+  </si>
+  <si>
+    <t>environment</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/allergy-intolerance-category</t>
+  </si>
+  <si>
+    <t>OTH</t>
   </si>
   <si>
     <t>other</t>
   </si>
   <si>
-    <t>Outras substâncias</t>
-  </si>
-  <si>
-    <t>environment</t>
-  </si>
-  <si>
-    <t>Fator Externo/Ambiental</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/allergy-intolerance-category</t>
+    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
   </si>
 </sst>
 </file>
@@ -402,7 +406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -454,23 +458,61 @@
         <v>37</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>39</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="B2" t="s" s="2">
         <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
